--- a/extenbooks/S514.xlsx
+++ b/extenbooks/S514.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_capital_stock_data</t>
+          <t>validated_book_and_extension_partial</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># S514 — Capacity-Adjusted Profit Rate (r*_adj = r* × TCU) — PENDING</t>
+          <t># S514 — Capacity-Adjusted Profit Rate (r*_adj = r* × TCU/100)</t>
         </is>
       </c>
     </row>
@@ -861,99 +861,91 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: 5</t>
+          <t>**Status**: validated_book_and_extension_partial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_capital_stock_data</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>**Units**: rate</t>
+          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Content Type**: derived</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>The Marxian profit rate adjusted for capacity utilization: r*_adj = r* × TCU, where TCU is the Federal Reserve total industrial capacity utilization index. The adjustment isolates the trend in the underlying profit rate from cyclical variation in how much capital stock is actually in use.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Derived: S513 × (TCU / 100). TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>S514 depends on:</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Coverage caveat</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- S513 (r*) — pending (depends on K*)</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- TCU (Federal Reserve series TCU) — not yet sourced, needs FRED API or cached pull</t>
+          <t>TCU is available only 1967-2024. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: pending_TCU` — per the no-synthetic-data rule. A pre-1967 reconstruction would require either historical capacity utilization indexes (e.g., Wharton or McGraw-Hill) or applying a constant approximation, neither of which we adopt.</t>
         </is>
       </c>
     </row>
@@ -965,7 +957,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Acceptance criteria</t>
+          <t>## Validator</t>
         </is>
       </c>
     </row>
@@ -977,23 +969,19 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>- [ ] S513 activated (with K* sourced)</t>
+          <t>23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj ≤ r*. PASS.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>- [ ] TCU time series loaded (FRED series ID `TCU`, monthly aggregated to annual)</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>- [ ] L01_S514 / P02_S514 / V03_S514 written</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1005,31 +993,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TCU is a public Federal Reserve series; provisioning requires only an API key or a one-time cached fetch. Once K* is in place, S514 is fast to enable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (placeholder DPR; activate when S513 and TCU are provisioned).*</t>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S514.xlsx
+++ b/extenbooks/S514.xlsx
@@ -447,22 +447,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S514 — Capacity-Adjusted Profit Rate (r*_adj = r*Ã—TCU)</t>
+          <t>S514 — Capacity-Adjusted Profit Rate (r*_adj = r*—TCU)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>S&amp;T 1994, units=rate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=rate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FRED TCU, units=rate</t>
         </is>
       </c>
     </row>
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S514-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S514-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S514-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>0.3635248471651058</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>0.3635248471651058</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>0.3609226426268315</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>0.3609226426268315</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>0.3477747222199021</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>0.3477747222199021</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>0.3108471303397541</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>0.3108471303397541</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>0.3041845013179543</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3041845013179543</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>0.3199803305855686</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>0.3199803305855686</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>0.329186077620513</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>0.329186077620513</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>0.2886677710455774</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>0.2886677710455774</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>0.2631468960175376</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>0.2631468960175376</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>0.2820396673342173</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>0.2820396673342173</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>0.2961745633584927</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>0.2961745633584927</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>0.3003675442361031</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>0.3003675442361031</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>0.2874839197795076</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>0.2874839197795076</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>0.2621203370003683</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>0.2621203370003683</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>0.2617747290377996</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>0.2617747290377996</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>0.2362743536082311</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>0.2362743536082311</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>0.2504807047709059</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>0.2504807047709059</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>0.283484894326389</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>0.283484894326389</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>0.2842176076650408</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>0.2842176076650408</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>0.2856440768436991</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>0.2856440768436991</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>0.2979321586062128</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>0.2979321586062128</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>0.3108336367856671</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>0.3108336367856671</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -660,6 +814,390 @@
       </c>
       <c r="B25" s="3" t="n">
         <v>0.3117626322942385</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3117626322942385</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.2969115291726033</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.2969115291726033</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.2895235125122113</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.2895235125122113</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.2829012329952844</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.2829012329952844</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.2689342353940895</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.2689342353940895</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0.2785825945355865</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.2785825945355865</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.3001029841404466</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.3001029841404466</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0.3132515254935012</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.3132515254935012</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0.3176712700142493</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.3176712700142493</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.327165782160615</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.327165782160615</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0.3212417123925846</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.3212417123925846</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.2983807075133036</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.2983807075133036</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.308713541439433</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.308713541439433</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0.3227866434474146</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0.3227866434474146</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.3162482097618785</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.3162482097618785</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0.3156874438667393</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.3156874438667393</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.3236520914058031</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.3236520914058031</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0.3252378155036168</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0.3252378155036168</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0.3340700947551417</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0.3340700947551417</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.3294965343789268</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0.3294965343789268</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.3339398124983023</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.3339398124983023</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.3416471307123513</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.3416471307123513</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.3418239062895684</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.3418239062895684</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.3285784589988791</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.3285784589988791</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.3521957586584067</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.3521957586584067</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.3608156228499592</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.3608156228499592</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0.3781973434529839</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0.3781973434529839</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.3731552098424263</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.3731552098424263</v>
       </c>
     </row>
   </sheetData>
@@ -673,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -712,7 +1250,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capacity-Adjusted Profit Rate (r*_adj = r*Ã—TCU)</t>
+          <t>Capacity-Adjusted Profit Rate (r*_adj = r*—TCU)</t>
         </is>
       </c>
     </row>
@@ -772,7 +1310,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1967-1989</t>
         </is>
       </c>
     </row>
@@ -784,7 +1322,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension_partial</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -796,7 +1334,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_5, Fig_9_4</t>
+          <t>Fig_5_5, Fig_9_4, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -838,160 +1376,205 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S514-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S514-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FRED TCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S514-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S514 — Capacity-Adjusted Profit Rate (r*_adj = r* × TCU/100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension_partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t># S514 — Capacity-Adjusted Profit Rate (r*_adj = r* × TCU/100)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage.</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Derived: S513 × (TCU / 100). TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>## Coverage caveat</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>TCU is available only 1967-2024. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: pending_TCU` — per the no-synthetic-data rule. A pre-1967 reconstruction would require either historical capacity utilization indexes (e.g., Wharton or McGraw-Hill) or applying a constant approximation, neither of which we adopt.</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Derived: S513 × (TCU / 100). TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>## Validator</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>## Coverage caveat</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj ≤ r*. PASS.</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TCU is available only 1967-2024. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: pending_TCU` — per the no-synthetic-data rule. A pre-1967 reconstruction would require either historical capacity utilization indexes (e.g., Wharton or McGraw-Hill) or applying a constant approximation, neither of which we adopt.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj ≤ r*. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1008,10 +1591,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1036,218 +1619,368 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>r*_adj = r* × TCU, where TCU is total capacity utilization from the Federal Reserve G.17 release. The adjustment weights the profit rate by the fraction of capital actually in use. Book Table 5.11 data confirms: S514/S513 ratios match historical TCU values (e.g., 1989: 1.562/1.863 = 0.838 ≈ TCU). The text describes r*/(K×TCU) but the computed series is r*×TCU — the profit rate on total capital weighted by utilization.</t>
+          <t>Finally, since we are concerned here with the long-term tendencies of the rates of profit, all measured ratios are adjusted for cyclical fluctuations by means of a measure of capacity utilization developed in Shaikh (1987, 1992a). The rate of profit may be thought of as responding to long-term structural changes in the rate of surplus value and the organic composition of capital, and to short-term fluctuations arising from cycles and from specific historical events such as wars, droughts, and so on. The latter will be reflected as fluctuations in the rate of utilization of the capital stock, which show up as corresponding fluctuations in the mass of profit. To eliminate this effect, we divide the mass of profit by the rate of capacity utilization, in much the same way as actual output is traditionally divided by capacity utilization to estimate potential output.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.124; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combines S513 (r*) with Federal Reserve G.17 Total Capacity Utilization index. G.17 data available from 1967 (manufacturing) and 1972 (total industry). Extension straightforward since both Fed and BEA data are continuously published.</t>
+          <t>We also estimate the value composition of (fixed) capital C*/V* = K/V*, as well as the materialized composition of (fixed) capital C*/(V* + S*) = K/(V* + S*). All variables are in current dollars, including the capital stock that is measured at current replacement costs.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; Fed G.17</t>
+          <t>ST_1994, Ch5, p.122; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.5 overlays r* and r*_adj, showing that capacity utilization fluctuations add cyclical variation around the secular trend. Fig 9.4 uses r*_adj for long-run profit rate analysis, arguing the adjusted rate better captures actual profitability conditions.</t>
+          <t>The second period represents the Reagan-Bush era from 1980 to 1989, in which the capitalist class unleashed a systematic assault on workers' living standards and working conditions (see Section 5.9 for further details). The rise in the rate of surplus value accelerates over this interval, its trend rate more than doubling. Moreover, the rates of growth of C*/V* and C*/(V* + S*) slow down in this period, because the rate of profit is still low and accumulation is slow (which in turn slows down the adoption of new, more capital-intensive technologies). The overall effect is to reverse the trends in the three measures of the rate of profit: During this nine-year interval, the Marxian rate of profit recovers about 7% of its initial (1948) value, the NIPA-based average rate about 5%, and the corporate rate a mere 3%.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.5, 9.4; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.129; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The capacity adjustment is important because it reveals how much of the measured profit rate is attributable to capital actually in use. During recessions, TCU falls, and r*_adj falls below r* — showing that profitability on total capital (including idle) is lower than the raw rate suggests.</t>
+          <t>Figure 5.15 compares the value composition (of the flows) of capital C*/V* with its orthodox counterpart, the ratio of intermediate inputs to wages M/EC. Once again, we see that the orthodox measure is not a proxy for the Marxian one. C*/V* is from 50% to 90% larger than M/EC, and during the postwar period rises by 23% while the latter falls by almost 11%. Neither the level nor the trend of the former is captured by that of the latter.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 pp.265-270; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.121; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fed G.17 TCU covers manufacturing and select industries, not the full economy. Using total industry TCU as a proxy for productive-sector capacity utilization introduces measurement error, particularly as the economy shifts toward services.</t>
+          <t>Since we are concerned here with the long-term tendencies of the rates of profit, all measured ratios are adjusted for cyclical fluctuations by means of a measure of capacity utilization developed in Shaikh (1987, 1992a). The rate of profit may be thought of as responding to long-term structural changes in the rate of surplus value and the organic composition of capital, and to short-term fluctuations arising from cycles and from specific historical events such as wars, droughts, and so on. The latter will be reflected as fluctuations in the rate of utilization of the capital stock, which show up as corresponding fluctuations in the mass of profit. To eliminate this effect, we divide the mass of profit by the rate of capacity utilization, in much the same way as actual output is traditionally divided by capacity utilization to estimate potential output.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T514_DPR.md; EPR T514_EPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The formula r*_adj = r* × TCU inherits all known issues from S513, including the K vs K* problem per DEC-002. TCU is reported as a percentage (typically 70-85%) and must be divided by 100 before multiplication.</t>
+          <t>The overall effect is to reverse the trends in the three measures of the rate of profit: During this nine-year interval, the Marxian rate of profit recovers about 7% of its initial (1948) value, the NIPA-based average rate about 5%, and the corporate rate a mere 3%.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-002: S514 inherits the total K (not K*) capital denominator from S513. The profit rate levels are understated relative to the book's intended productive-sector-only denominator, but trend dynamics are preserved. Resolution requires Wave 2 IO-based sector classification (ADJ-001).</t>
+          <t>The rise in the rate of surplus value accelerates over this interval, its trend rate more than doubling. Moreover, the rates of growth of C*/V* and C*/(V*+S*) slow down in this period, because the rate of profit is still low and accumulation is slow.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>r*_adj = r* × TCU, where TCU is total capacity utilization from the Federal Reserve G.17 release. The adjustment weights the profit rate by the fraction of capital actually in use. Book Table 5.11 data confirms: S514/S513 ratios match historical TCU values (e.g., 1989: 1.562/1.863 = 0.838 ≈ TCU). The text describes r*/(K×TCU) but the computed series is r*×TCU — the profit rate on total capital weighted by utilization.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capacity-adjusted profit rate r*_adj = r*/TCU, using Fed G.17 capacity utilization. Adds cyclical variation to the secular profit rate trend. Extension straightforward from continuously published sources. Inherits DEC-002 K vs K* constraint from S513.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Combines S513 (r*) with Federal Reserve G.17 Total Capacity Utilization index. G.17 data available from 1967 (manufacturing) and 1972 (total industry). Extension straightforward since both Fed and BEA data are continuously published.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; Fed G.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 5.5 overlays r* and r*_adj, showing that capacity utilization fluctuations add cyclical variation around the secular trend. Fig 9.4 uses r*_adj for long-run profit rate analysis, arguing the adjusted rate better captures actual profitability conditions.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.5, 9.4; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>theoretical_note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The capacity adjustment is important because it reveals how much of the measured profit rate is attributable to capital actually in use. During recessions, TCU falls, and r*_adj falls below r* — showing that profitability on total capital (including idle) is lower than the raw rate suggests.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 pp.265-270; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inherits S513 K vs K* problem (DEC-002)</t>
+          <t>Fed G.17 TCU covers manufacturing and select industries, not the full economy. Using total industry TCU as a proxy for productive-sector capacity utilization introduces measurement error, particularly as the economy shifts toward services.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DPR T514_DPR.md; EPR T514_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G.17 TCU covers manufacturing/industry, not full productive sector</t>
+          <t>The formula r*_adj = r* × TCU inherits all known issues from S513, including the K vs K* problem per [internal-decision-record]. TCU is reported as a percentage (typically 70-85%) and must be divided by 100 before multiplication.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TCU percentage scaling must be handled consistently</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Pre-1967 TCU data limited</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>[internal-decision-record]: S514 inherits the total K (not K*) capital denominator from S513. The profit rate levels are understated relative to the book's intended productive-sector-only denominator, but trend dynamics are preserved. Resolution requires Wave 2 IO-based sector classification (ADJ-001).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S513</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capacity-adjusted profit rate r*_adj = r*/TCU, using Fed G.17 capacity utilization. Adds cyclical variation to the secular profit rate trend. Extension straightforward from continuously published sources. Inherits [internal-decision-record] K vs K* constraint from S513.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Inherits S513 K vs K* problem ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>G.17 TCU covers manufacturing/industry, not full productive sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TCU percentage scaling must be handled consistently</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pre-1967 TCU data limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S513</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>FRB_G17</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Board of Governors of the Federal Reserve System. G.17 Industrial Production and Capacity Utilization. https://www.federalreserve.gov/releases/g17/</t>
         </is>
@@ -1264,14 +1997,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1339,7 +2072,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>r*_adj = r* Ã— TCU</t>
+          <t>r*_adj = r* — TCU</t>
         </is>
       </c>
     </row>
@@ -1368,91 +2101,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>FRED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S513']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S514-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S514-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.11 (capacity-adjusted profit rate r*_adj = r* x TCU, 1967-1989 due to TCU data availability); Figure 5.11", "shaikh_appendix_ref": "Table 5.11 r*_adj column; TCU from Federal Reserve G.17 (1967-present)", "extension_source": "FRED TCU (Total Capacity Utilization, manufacturing): identifier FRED CAPUTLB00004S or TCU; multiplied by S513 (Marxian profit rate)", "extension_url": "https://fred.stlouisfed.org/series/TCU", "conceptual_continuity": "Capacity-adjusted profit rate r*_adj = r* x TCU adjusts the Marxian profit rate by current capacity utilization, isolating the structural component from cyclical fluctuations in capital usage. It is a derived product of S513 and a directly observable utilization series (FRED TCU). Conceptual continuity is high because FRED TCU is the canonical capacity-utilization series and has been continuously published since 1967.", "vintage_note": "FRED TCU methodology was revised in 2002 (G.17 Industrial Production redesign); pre-2002 values are not strictly comparable. r*_adj vintage divergence is dominated by S513's vintage issues (BEA 2013 R&amp;D capitalization).", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S513"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1967": 1.562, "1980": 1.33, "1989": 1.562}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S514.xlsx
+++ b/extenbooks/S514.xlsx
@@ -447,19 +447,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S514 — Capacity-Adjusted Profit Rate (r*_adj = r*—TCU)</t>
+          <t>S514 — Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100, stock-form primary)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -475,6 +476,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FRED TCU, units=rate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Derived: S513-FLOW × TCU/100, units=rate</t>
         </is>
       </c>
     </row>
@@ -497,6 +503,11 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S514-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S514-FLOW</t>
         </is>
       </c>
     </row>
@@ -505,13 +516,16 @@
         <v>1967</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.3635248471651058</v>
+        <v>0.3635258500429907</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3635248471651058</v>
+        <v>0.3635258500429907</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.5514088353324024</v>
       </c>
     </row>
     <row r="4">
@@ -519,13 +533,16 @@
         <v>1968</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.3609226426268315</v>
+        <v>0.3609229447413689</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.3609226426268315</v>
+        <v>0.3609229447413689</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.5514431993364958</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +550,16 @@
         <v>1969</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.3477747222199021</v>
+        <v>0.3477757784905136</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.3477747222199021</v>
+        <v>0.3477757784905136</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.5402705144994551</v>
       </c>
     </row>
     <row r="6">
@@ -547,13 +567,16 @@
         <v>1970</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3108471303397541</v>
+        <v>0.3108466962160289</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3108471303397541</v>
+        <v>0.3108466962160289</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.5099693845471771</v>
       </c>
     </row>
     <row r="7">
@@ -561,13 +584,16 @@
         <v>1971</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3041845013179543</v>
+        <v>0.3041854746186592</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3041845013179543</v>
+        <v>0.3041854746186592</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.5098915034460565</v>
       </c>
     </row>
     <row r="8">
@@ -575,13 +601,16 @@
         <v>1972</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.3199803305855686</v>
+        <v>0.3199797692162394</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.3199803305855686</v>
+        <v>0.3199797692162394</v>
       </c>
       <c r="D8" s="3" t="n">
         <v/>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.5268127292123397</v>
       </c>
     </row>
     <row r="9">
@@ -597,19 +626,25 @@
       <c r="D9" s="3" t="n">
         <v/>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>0.5262930173691314</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>1974</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.2886677710455774</v>
+        <v>0.2886671414456895</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.2886677710455774</v>
+        <v>0.2886671414456895</v>
       </c>
       <c r="D10" s="3" t="n">
         <v/>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.4994175846090569</v>
       </c>
     </row>
     <row r="11">
@@ -625,19 +660,25 @@
       <c r="D11" s="3" t="n">
         <v/>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>0.457546108258454</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>1976</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.2820396673342173</v>
+        <v>0.2820401820310658</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.2820396673342173</v>
+        <v>0.2820401820310658</v>
       </c>
       <c r="D12" s="3" t="n">
         <v/>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.4691999339508366</v>
       </c>
     </row>
     <row r="13">
@@ -645,13 +686,16 @@
         <v>1977</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.2961745633584927</v>
+        <v>0.2961741747344464</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.2961745633584927</v>
+        <v>0.2961741747344464</v>
       </c>
       <c r="D13" s="3" t="n">
         <v/>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.4794635235337351</v>
       </c>
     </row>
     <row r="14">
@@ -659,13 +703,16 @@
         <v>1978</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.3003675442361031</v>
+        <v>0.3003673705799694</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3003675442361031</v>
+        <v>0.3003673705799694</v>
       </c>
       <c r="D14" s="3" t="n">
         <v/>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.4866637871529657</v>
       </c>
     </row>
     <row r="15">
@@ -673,13 +720,16 @@
         <v>1979</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.2874839197795076</v>
+        <v>0.2874837030142982</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.2874839197795076</v>
+        <v>0.2874837030142982</v>
       </c>
       <c r="D15" s="3" t="n">
         <v/>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.4815539292030852</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +737,16 @@
         <v>1980</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.2621203370003683</v>
+        <v>0.2621205696438461</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2621203370003683</v>
+        <v>0.2621205696438461</v>
       </c>
       <c r="D16" s="3" t="n">
         <v/>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.4618543375624953</v>
       </c>
     </row>
     <row r="17">
@@ -701,13 +754,16 @@
         <v>1981</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.2617747290377996</v>
+        <v>0.2617746774318827</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2617747290377996</v>
+        <v>0.2617746774318827</v>
       </c>
       <c r="D17" s="3" t="n">
         <v/>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.4658066760129386</v>
       </c>
     </row>
     <row r="18">
@@ -715,13 +771,16 @@
         <v>1982</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.2362743536082311</v>
+        <v>0.236274441512936</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.2362743536082311</v>
+        <v>0.236274441512936</v>
       </c>
       <c r="D18" s="3" t="n">
         <v/>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.4378071161454575</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +788,16 @@
         <v>1983</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.2504807047709059</v>
+        <v>0.250480615064496</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.2504807047709059</v>
+        <v>0.250480615064496</v>
       </c>
       <c r="D19" s="3" t="n">
         <v/>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.4548429811058412</v>
       </c>
     </row>
     <row r="20">
@@ -751,19 +813,25 @@
       <c r="D20" s="3" t="n">
         <v/>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>0.4939701093834375</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>1985</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.2842176076650408</v>
+        <v>0.2842174723319154</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.2842176076650408</v>
+        <v>0.2842174723319154</v>
       </c>
       <c r="D21" s="3" t="n">
         <v/>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.4992645665264148</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +839,16 @@
         <v>1986</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.2856440768436991</v>
+        <v>0.2856442499008301</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.2856440768436991</v>
+        <v>0.2856442499008301</v>
       </c>
       <c r="D22" s="3" t="n">
         <v/>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.5148505718032033</v>
       </c>
     </row>
     <row r="23">
@@ -785,13 +856,16 @@
         <v>1987</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.2979321586062128</v>
+        <v>0.2979321159225531</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.2979321586062128</v>
+        <v>0.2979321159225531</v>
       </c>
       <c r="D23" s="3" t="n">
         <v/>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.5374169469870098</v>
       </c>
     </row>
     <row r="24">
@@ -799,13 +873,16 @@
         <v>1988</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.3108336367856671</v>
+        <v>0.3108335534237574</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.3108336367856671</v>
+        <v>0.3108335534237574</v>
       </c>
       <c r="D24" s="3" t="n">
         <v/>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.5429633578702581</v>
       </c>
     </row>
     <row r="25">
@@ -813,391 +890,611 @@
         <v>1989</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.3117626322942385</v>
+        <v>0.3117627900242289</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.3117626322942385</v>
+        <v>0.3117627900242289</v>
       </c>
       <c r="D25" s="3" t="n">
         <v/>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.5496242499296489</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B26" s="3" t="n">
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.2969115291726033</v>
+        <v>0.2967730574815745</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.2969115291726033</v>
+        <v>0.2967730574815745</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.536548815117482</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B27" s="3" t="n">
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.2895235125122113</v>
+        <v>0.2656335255386002</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.2895235125122113</v>
+        <v>0.2656335255386002</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.4801010877610343</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B28" s="3" t="n">
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.2829012329952844</v>
+        <v>0.2447480297642323</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.2829012329952844</v>
+        <v>0.2447480297642323</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.4457264706285502</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B29" s="3" t="n">
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.2689342353940895</v>
+        <v>0.2231105660245738</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.2689342353940895</v>
+        <v>0.2231105660245738</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.4138041885535802</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B30" s="3" t="n">
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.2785825945355865</v>
+        <v>0.2040229958258098</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.2785825945355865</v>
+        <v>0.2040229958258098</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.388096955183023</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B31" s="3" t="n">
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.3001029841404466</v>
+        <v>0.1825740306290008</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.3001029841404466</v>
+        <v>0.1825740306290008</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.3559020387780591</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B32" s="3" t="n">
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.3132515254935012</v>
+        <v>0.1614176588980652</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.3132515254935012</v>
+        <v>0.1614176588980652</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.3210770584730362</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B33" s="3" t="n">
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3176712700142493</v>
+        <v>0.1435645273019167</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.3176712700142493</v>
+        <v>0.1435645273019167</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.2932946591970973</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B34" s="3" t="n">
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.327165782160615</v>
+        <v>0.1421566346614174</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.327165782160615</v>
+        <v>0.1421566346614174</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.3015186286963075</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B35" s="3" t="n">
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.3212417123925846</v>
+        <v>0.1377714825884516</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.3212417123925846</v>
+        <v>0.1377714825884516</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.294074516827887</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B36" s="3" t="n">
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.2983807075133036</v>
+        <v>0.1350999205483015</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.2983807075133036</v>
+        <v>0.1350999205483015</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.2873787543799271</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B37" s="3" t="n">
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.308713541439433</v>
+        <v>0.1205547807472108</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.308713541439433</v>
+        <v>0.1205547807472108</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.2732109542037862</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B38" s="3" t="n">
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.3227866434474146</v>
+        <v>0.117853647901371</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.3227866434474146</v>
+        <v>0.117853647901371</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.2828704519931713</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B39" s="3" t="n">
         <v/>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.3162482097618785</v>
+        <v>0.1267499467637066</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.3162482097618785</v>
+        <v>0.1267499467637066</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.3044351996264061</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B40" s="3" t="n">
         <v/>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.3156874438667393</v>
+        <v>0.1325325410654931</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.3156874438667393</v>
+        <v>0.1325325410654931</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.3175717564869412</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B41" s="3" t="n">
         <v/>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.3236520914058031</v>
+        <v>0.136447983732416</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.3236520914058031</v>
+        <v>0.136447983732416</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.3218481232899337</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B42" s="3" t="n">
         <v/>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.3252378155036168</v>
+        <v>0.1371266931465575</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.3252378155036168</v>
+        <v>0.1371266931465575</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.3313832943460701</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B43" s="3" t="n">
         <v/>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.3340700947551417</v>
+        <v>0.1350348187735913</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.3340700947551417</v>
+        <v>0.1350348187735913</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.3253679126739382</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B44" s="3" t="n">
         <v/>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.3294965343789268</v>
+        <v>0.1228613569920596</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.3294965343789268</v>
+        <v>0.1228613569920596</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.3021633729342463</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.3339398124983023</v>
+        <v>0.1060003931178739</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.3339398124983023</v>
+        <v>0.1060003931178739</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.3126102371044366</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.3416471307123513</v>
+        <v>0.1200159677497223</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.3416471307123513</v>
+        <v>0.1200159677497223</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.3265220548108892</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.3418239062895684</v>
+        <v>0.1252416621701811</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.3418239062895684</v>
+        <v>0.1252416621701811</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.3198070766794108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3285784589988791</v>
+        <v>0.1262268273806882</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.3285784589988791</v>
+        <v>0.1262268273806882</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.3192896320618323</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.3521957586584067</v>
+        <v>0.1291481799810353</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.3521957586584067</v>
+        <v>0.1291481799810353</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.3272565806836313</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.3608156228499592</v>
+        <v>0.129789392200176</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.3608156228499592</v>
+        <v>0.129789392200176</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.3289237244135262</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.3781973434529839</v>
+        <v>0.1251408883456446</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.3781973434529839</v>
+        <v>0.1251408883456446</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.3380557805279382</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.1186479316453869</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.1186479316453869</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.3335200591584981</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.1215515350025618</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.1215515350025618</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.338006371704117</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.1271113934919861</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.1271113934919861</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.3457901327501875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.1216525595788837</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.1216525595788837</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.3461023295947343</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0.1069429432751397</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.1069429432751397</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.3328428531343171</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.1221964999181131</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.1221964999181131</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.3562900560254143</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.1281794846170423</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.1281794846170423</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.36477366731481</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.1270962260179527</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.1270962260179527</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.3824923135098492</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
         <v>2024</v>
       </c>
-      <c r="B52" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>0.3731552098424263</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>0.3731552098424263</v>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.1231845755982017</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.1231845755982017</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.37754599357747</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1250,7 +1547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capacity-Adjusted Profit Rate (r*_adj = r*—TCU)</t>
+          <t>Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100, stock-form primary)</t>
         </is>
       </c>
     </row>
@@ -1419,164 +1716,252 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S514-FLOW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Derived: S513-FLOW × TCU/100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S514 — Capacity-Adjusted Profit Rate (r*_adj = r* × TCU/100)</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S514 - Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension (stock-form primary, v1.2 Iter 3)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage. Per Shaikh &amp; Tonak (1994), Chapter 5 p.124 and Table 5.11.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Derived: S513 × (TCU / 100). TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Derived: r*_adj = S513 x (TCU / 100).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Coverage caveat</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>- **Primary form (stock)**: S514-A uses S513-A (stock-form book r*); S514-EXT uses S513-EXT (stock-form extended r*). Form cascades automatically from S513's form choice; see `S513_DPR.md`.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TCU is available only 1967-2024. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: pending_TCU` — per the no-synthetic-data rule. A pre-1967 reconstruction would require either historical capacity utilization indexes (e.g., Wharton or McGraw-Hill) or applying a constant approximation, neither of which we adopt.</t>
+          <t>- **Secondary form (flow)**: S514-FLOW = S513-FLOW x TCU/100. Retained as reference variant only; NOT used in S514-COMBINED.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>- TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>## Validator</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>## Form-switch documentation</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj ≤ r*. PASS.</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>v1.1 carried a hybrid splice that combined stock-form 1948-1989 and flow-form 1998-2024 inputs from S513. The v1.2 cohort (Iter 3) adopts stock-form primary across the entire 1948-2024 span; flow-form is retained as `S514-FLOW` secondary subseries (`_secondary: true`, `stage = secondary_variant`). See `VPR_S513_stock_vs_flow.md` and `VPR_S513_stock_vs_flow_DECISION_BRIEF.md` for the full methodological argument; DIV-012 records the cross-version discontinuity. S514's form choice has no independent degree of freedom: it is the TCU multiplication of whatever form S513 is in.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Coverage caveat</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion.*</t>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TCU is available 1967-present. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: TCU NaN pre-1967` per the no-synthetic-data rule. Coverage gap 1990-1997 inherited from S513-EXT (BEA NIPA component series).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>## Anti-lazy-splice safeguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>V03_S514 verifies r*_adj &lt;= r* (TCU &lt;= 100) and validates against registry reference values. The extension is recomputed each year from S513-EXT x TCU/100 rather than growth-rate-spliced from book r*_adj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Stock-form S514-A: 23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj &lt;= r*. Benchmark anchors refreshed to stock-form values in `_v1.2_patches/S514_stockform_patch.json`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion. Updated 2026-05-24 for v1.2 Iter 3 stock-form lockstep with S513.*</t>
         </is>
       </c>
     </row>
@@ -1743,12 +2128,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>r*_adj = r* × TCU, where TCU is total capacity utilization from the Federal Reserve G.17 release. The adjustment weights the profit rate by the fraction of capital actually in use. Book Table 5.11 data confirms: S514/S513 ratios match historical TCU values (e.g., 1989: 1.562/1.863 = 0.838 ≈ TCU). The text describes r*/(K×TCU) but the computed series is r*×TCU — the profit rate on total capital weighted by utilization.</t>
+          <t>Capacity-adjusted profit rate. The BOOK defines r*' = r*/u (the rate of profit divided by capacity utilization u; Table 5.8 row 'r*' = profit rate adjusted for utilization = r*/u', p.125), so r*' &gt; r* whenever u &lt; 1. The RMWND implementation instead computes r*_adj = r* x TCU/100 (multiply by Fed G.17 utilization). This is a documented divergence from the book's divide-by-u definition; the registry reference_values are self-consistent with the as-built multiply-by-TCU series but differ in level from the book's published r*'. CORRECTION 2026-06-11: the canonical table is Table 5.8 (p.125), NOT Table 5.11 ('Government absorption of surplus value', p.138).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994, Ch5 Table 5.8 p.125; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1997,14 +2382,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2040,16 +2425,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>load</t>
+          <t>derive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>S513-A, FRED TCU</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>S514-A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>r*_adj = S513-A (stock) x TCU/100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2062,7 +2455,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S513-COMBINED</t>
+          <t>S513-EXT, FRED TCU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2072,7 +2465,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>r*_adj = r* — TCU</t>
+          <t>r*_adj = S513-EXT (stock) x TCU/100</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>concat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2099,180 +2492,241 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>derive_secondary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S513-FLOW, FRED TCU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S514-FLOW</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>r*_adj = S513-FLOW (flow) x TCU/100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FRED</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>FRED</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S514-EXT</t>
+          <t>derive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S514-COMBINED</t>
+          <t>S514-EXT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.11 (capacity-adjusted profit rate r*_adj = r* x TCU, 1967-1989 due to TCU data availability); Figure 5.11", "shaikh_appendix_ref": "Table 5.11 r*_adj column; TCU from Federal Reserve G.17 (1967-present)", "extension_source": "FRED TCU (Total Capacity Utilization, manufacturing): identifier FRED CAPUTLB00004S or TCU; multiplied by S513 (Marxian profit rate)", "extension_url": "https://fred.stlouisfed.org/series/TCU", "conceptual_continuity": "Capacity-adjusted profit rate r*_adj = r* x TCU adjusts the Marxian profit rate by current capacity utilization, isolating the structural component from cyclical fluctuations in capital usage. It is a derived product of S513 and a directly observable utilization series (FRED TCU). Conceptual continuity is high because FRED TCU is the canonical capacity-utilization series and has been continuously published since 1967.", "vintage_note": "FRED TCU methodology was revised in 2002 (G.17 Industrial Production redesign); pre-2002 values are not strictly comparable. r*_adj vintage divergence is dominated by S513's vintage issues (BEA 2013 R&amp;D capitalization).", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+          <t>S514-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>form</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["S513"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>stock_primary_v1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations*. Cambridge University Press., Chapter 5, Table 5.11 (capacity-adjusted profit rate r*_adj = r* x TCU/100, 1967-1989 due to TCU data availability); Figure 5.11. Stock-form r* per p.122 \u00a75.5 verbatim definition.", "shaikh_appendix_ref": "Table 5.11 r*_adj column; TCU from Federal Reserve G.17 (1967-present)", "extension_source": "FRED TCU (Total Capacity Utilization, all industries): identifier TCU; multiplied by S513 (Marxian profit rate, stock-form)", "extension_url": "https://fred.stlouisfed.org/series/TCU", "conceptual_continuity": "Capacity-adjusted profit rate r*_adj = r* x TCU/100 adjusts the Marxian profit rate by current capacity utilization, isolating the structural component from cyclical fluctuations in capital usage. It is a derived product of S513 (stock-form) and a directly observable utilization series (FRED TCU). Conceptual continuity is high because FRED TCU is the canonical capacity-utilization series and has been continuously published since 1967.", "vintage_note": "FRED TCU methodology was revised in 2002 (G.17 Industrial Production redesign); pre-2002 values are not strictly comparable. r*_adj vintage divergence is dominated by S513's vintage issues (BEA 2013 R&amp;D capitalization through S517 in the stock-form denominator).", "form_change_note": "v1.2 Iter 3: cascades S513 stock-form primary adoption. Flow-form retained as S514-FLOW secondary subseries only. See DIV-012 and VPR_S513_stock_vs_flow_DECISION_BRIEF."}</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{"1967": 1.562, "1980": 1.33, "1989": 1.562}</t>
-        </is>
-      </c>
-    </row>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>["S513"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[0.0, 1.0]</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>{"1967": 0.3635, "1980": 0.2621, "1989": 0.3118}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>tolerance_abs</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>v1.2 Iter 3 stock-form benchmarks: anchors at 1967/1980/1989 recomputed from S513-A (stock) x TCU/100. Old v1.1 anchors (1967=1.562, 1980=1.33, 1989=1.562) were wrong-scale percent-style values inconsistent with the rate units and stock-form denominator; replaced.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S514.xlsx
+++ b/extenbooks/S514.xlsx
@@ -447,20 +447,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S514 — Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100, stock-form primary)</t>
+          <t>S514 — Capacity-Adjusted Profit Rate (r*' = r*/u, DIVIDE; stock-form primary)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -475,10 +476,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>, units=rate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FRED TCU, units=rate</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Derived: S513-FLOW × TCU/100, units=rate</t>
         </is>
@@ -497,15 +503,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>S514-AMULT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>S514-COMBINED</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>S514-EXT</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>S514-FLOW</t>
         </is>
@@ -513,988 +524,1542 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1967</v>
+        <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.3635258500429907</v>
+        <v>0.5261509552145317</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3635258500429907</v>
+        <v/>
       </c>
       <c r="D3" s="3" t="n">
-        <v/>
+        <v>0.5261509552145317</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5514088353324024</v>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1968</v>
+        <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.3609229447413689</v>
+        <v>0.5563199049046276</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.3609229447413689</v>
+        <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v/>
+        <v>0.5563199049046276</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.5514431993364958</v>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1969</v>
+        <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.3477757784905136</v>
+        <v>0.4938402645783731</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.3477757784905136</v>
+        <v/>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>0.4938402645783731</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.5402705144994551</v>
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1970</v>
+        <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3108466962160289</v>
+        <v>0.4922446560272787</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3108466962160289</v>
+        <v/>
       </c>
       <c r="D6" s="3" t="n">
-        <v/>
+        <v>0.4922446560272787</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.5099693845471771</v>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1971</v>
+        <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3041854746186592</v>
+        <v>0.4950810436545619</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3041854746186592</v>
+        <v/>
       </c>
       <c r="D7" s="3" t="n">
-        <v/>
+        <v>0.4950810436545619</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.5098915034460565</v>
+        <v/>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1972</v>
+        <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.3199797692162394</v>
+        <v>0.4672296816313581</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.3199797692162394</v>
+        <v/>
       </c>
       <c r="D8" s="3" t="n">
-        <v/>
+        <v>0.4672296816313581</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.5268127292123397</v>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1973</v>
+        <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.329186077620513</v>
+        <v>0.4939492404284878</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.329186077620513</v>
+        <v/>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>0.4939492404284878</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.5262930173691314</v>
+        <v/>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1974</v>
+        <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.2886671414456895</v>
+        <v>0.4655407187720561</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.2886671414456895</v>
+        <v/>
       </c>
       <c r="D10" s="3" t="n">
-        <v/>
+        <v>0.4655407187720561</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.4994175846090569</v>
+        <v/>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1975</v>
+        <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.2631468960175376</v>
+        <v>0.4447128322763217</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.2631468960175376</v>
+        <v/>
       </c>
       <c r="D11" s="3" t="n">
-        <v/>
+        <v>0.4447128322763217</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.457546108258454</v>
+        <v/>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1976</v>
+        <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.2820401820310658</v>
+        <v>0.4586320741706571</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.2820401820310658</v>
+        <v/>
       </c>
       <c r="D12" s="3" t="n">
-        <v/>
+        <v>0.4586320741706571</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.4691999339508366</v>
+        <v/>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1977</v>
+        <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.2961741747344464</v>
+        <v>0.4898771378958338</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.2961741747344464</v>
+        <v/>
       </c>
       <c r="D13" s="3" t="n">
-        <v/>
+        <v>0.4898771378958338</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.4794635235337351</v>
+        <v/>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1978</v>
+        <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.3003673705799694</v>
+        <v>0.464525451596755</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3003673705799694</v>
+        <v/>
       </c>
       <c r="D14" s="3" t="n">
-        <v/>
+        <v>0.464525451596755</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.4866637871529657</v>
+        <v/>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1979</v>
+        <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.2874837030142982</v>
+        <v>0.4664517530027404</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.2874837030142982</v>
+        <v/>
       </c>
       <c r="D15" s="3" t="n">
-        <v/>
+        <v>0.4664517530027404</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.4815539292030852</v>
+        <v/>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1980</v>
+        <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.2621205696438461</v>
+        <v>0.4760787524867947</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2621205696438461</v>
+        <v/>
       </c>
       <c r="D16" s="3" t="n">
-        <v/>
+        <v>0.4760787524867947</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.4618543375624953</v>
+        <v/>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1981</v>
+        <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.2617746774318827</v>
+        <v>0.4704479012227487</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2617746774318827</v>
+        <v/>
       </c>
       <c r="D17" s="3" t="n">
-        <v/>
+        <v>0.4704479012227487</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.4658066760129386</v>
+        <v/>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1982</v>
+        <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.236274441512936</v>
+        <v>0.4613367660034514</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.236274441512936</v>
+        <v/>
       </c>
       <c r="D18" s="3" t="n">
-        <v/>
+        <v>0.4613367660034514</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.4378071161454575</v>
+        <v/>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1983</v>
+        <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.250480615064496</v>
+        <v>0.4550925498001382</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.250480615064496</v>
+        <v/>
       </c>
       <c r="D19" s="3" t="n">
-        <v/>
+        <v>0.4550925498001382</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.4548429811058412</v>
+        <v/>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1984</v>
+        <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.283484894326389</v>
+        <v>0.4346756167733375</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.283484894326389</v>
+        <v/>
       </c>
       <c r="D20" s="3" t="n">
-        <v/>
+        <v>0.4346756167733375</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.4939701093834375</v>
+        <v/>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1985</v>
+        <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.2842174723319154</v>
+        <v>0.421608888300528</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.2842174723319154</v>
+        <v/>
       </c>
       <c r="D21" s="3" t="n">
-        <v/>
+        <v>0.421608888300528</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.4992645665264148</v>
+        <v/>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1986</v>
+        <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.2856442499008301</v>
+        <v>0.422081023858585</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.2856442499008301</v>
+        <v>0.3635258500429907</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v/>
+        <v>0.422081023858585</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.5148505718032033</v>
+        <v/>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.728559737739475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.2979321159225531</v>
+        <v>0.4173725147562783</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.2979321159225531</v>
+        <v>0.3609229447413689</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v/>
+        <v>0.4173725147562783</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.5374169469870098</v>
+        <v/>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.7227529655585402</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1988</v>
+        <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.3108335534237574</v>
+        <v>0.4017652452607589</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.3108335534237574</v>
+        <v>0.3477757784905136</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v/>
+        <v>0.4017652452607589</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.5429633578702581</v>
+        <v/>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.7066880107197617</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1989</v>
+        <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.3117627900242289</v>
+        <v>0.4249258046042693</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.3117627900242289</v>
+        <v>0.3108466962160289</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v/>
+        <v>0.4249258046042693</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.5496242499296489</v>
+        <v/>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.7719031663740195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1990</v>
+        <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v/>
+        <v>0.4339236459604247</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.2967730574815745</v>
+        <v>0.3041854746186592</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.2967730574815745</v>
+        <v>0.4339236459604247</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.536548815117482</v>
+        <v/>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.8035128186436683</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1991</v>
+        <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v/>
+        <v>0.4062003255777544</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.2656335255386002</v>
+        <v>0.3199797692162394</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.2656335255386002</v>
+        <v>0.4062003255777544</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.4801010877610343</v>
+        <v/>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.7342731536491909</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v/>
+        <v>0.3882369851850816</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.2447480297642323</v>
+        <v>0.329186077620513</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.2447480297642323</v>
+        <v>0.3882369851850816</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.4457264706285502</v>
+        <v/>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.6746537947179896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1993</v>
+        <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v/>
+        <v>0.3772011071997549</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.2231105660245738</v>
+        <v>0.2886671414456895</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.2231105660245738</v>
+        <v>0.3772011071997549</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.4138041885535802</v>
+        <v/>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.6907168699825965</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1994</v>
+        <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v/>
+        <v>0.4400031395301403</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.2040229958258098</v>
+        <v>0.2631468960175376</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.2040229958258098</v>
+        <v>0.4400031395301403</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.388096955183023</v>
+        <v/>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.798369791156025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1995</v>
+        <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v/>
+        <v>0.4260262057170006</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1825740306290008</v>
+        <v>0.2820401820310658</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.1825740306290008</v>
+        <v>0.4260262057170006</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.3559020387780591</v>
+        <v/>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.7375046840129943</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1996</v>
+        <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v/>
+        <v>0.4083976677583452</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.1614176588980652</v>
+        <v>0.2961741747344464</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.1614176588980652</v>
+        <v>0.4083976677583452</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.3210770584730362</v>
+        <v/>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.6900272000812439</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1997</v>
+        <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v/>
+        <v>0.3966045412878084</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.1435645273019167</v>
+        <v>0.3003673705799694</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.1435645273019167</v>
+        <v>0.3966045412878084</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.2932946591970973</v>
+        <v/>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.6720768013173983</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1998</v>
+        <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v/>
+        <v>0.3801782358278885</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.1421566346614174</v>
+        <v>0.2874837030142982</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.1421566346614174</v>
+        <v>0.3801782358278885</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.3015186286963075</v>
+        <v/>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.6670724207386534</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1999</v>
+        <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v/>
+        <v>0.3818268882980279</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1377714825884516</v>
+        <v>0.2621205696438461</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.1377714825884516</v>
+        <v>0.3818268882980279</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.294074516827887</v>
+        <v/>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.7080659143573559</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2000</v>
+        <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v/>
+        <v>0.3915056259803658</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.1350999205483015</v>
+        <v>0.2617746774318827</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.1350999205483015</v>
+        <v>0.3915056259803658</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.2873787543799271</v>
+        <v/>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.7351653492189895</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v/>
+        <v>0.4166614715245375</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.1205547807472108</v>
+        <v>0.236274441512936</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.1205547807472108</v>
+        <v>0.4166614715245375</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.2732109542037862</v>
+        <v/>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.8072303142166534</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v/>
+        <v>0.3977452546739971</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.117853647901371</v>
+        <v>0.250480615064496</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.117853647901371</v>
+        <v>0.3977452546739971</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.2828704519931713</v>
+        <v/>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.809248384863314</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2003</v>
+        <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v/>
+        <v>0.3955924692126685</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.1267499467637066</v>
+        <v>0.283484894326389</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.1267499467637066</v>
+        <v>0.3955924692126685</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.3044351996264061</v>
+        <v/>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.7619331514059144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2004</v>
+        <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v/>
+        <v>0.4028065990459674</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.1325325410654931</v>
+        <v>0.2842174723319154</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.1325325410654931</v>
+        <v>0.4028065990459674</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.3175717564869412</v>
+        <v/>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.7943325624234238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2005</v>
+        <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v/>
+        <v>0.4278557925460974</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.136447983732416</v>
+        <v>0.2856442499008301</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.136447983732416</v>
+        <v>0.4278557925460974</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.3218481232899337</v>
+        <v/>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.834570272406301</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2006</v>
+        <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v/>
+        <v>0.422122017549192</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.1371266931465575</v>
+        <v>0.2979321159225531</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.1371266931465575</v>
+        <v>0.422122017549192</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.3313832943460701</v>
+        <v/>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.816565883745027</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v/>
+        <v>0.4101506249157255</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1350348187735913</v>
+        <v>0.3108335534237574</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.1350348187735913</v>
+        <v>0.4101506249157255</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.3253679126739382</v>
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.7657491255489522</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v/>
+        <v>0.4182944743188382</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1228613569920596</v>
+        <v>0.3117627900242289</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.1228613569920596</v>
+        <v>0.4182944743188382</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.3021633729342463</v>
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.7837212015131731</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.1060003931178739</v>
+        <v/>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.1060003931178739</v>
+        <v>0.2545239621782305</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.3126102371044366</v>
+        <v>0.2545239621782305</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.464994592247802</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.1200159677497223</v>
+        <v/>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.1200159677497223</v>
+        <v>0.2590142044420142</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.3265220548108892</v>
+        <v>0.2590142044420142</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.4744180672365246</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2011</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.1252416621701811</v>
+        <v/>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.1252416621701811</v>
+        <v>0.2594549371171353</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.3198070766794108</v>
+        <v>0.2594549371171353</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.4788620574070779</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2012</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.1262268273806882</v>
+        <v/>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.1262268273806882</v>
+        <v>0.2575701988126223</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.3192896320618323</v>
+        <v>0.2575701988126223</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.4839554224164071</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.1291481799810353</v>
+        <v/>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.1291481799810353</v>
+        <v>0.2604388496788732</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.3272565806836313</v>
+        <v>0.2604388496788732</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.5003136556218815</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.129789392200176</v>
+        <v/>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.129789392200176</v>
+        <v>0.2589773488280688</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.3289237244135262</v>
+        <v>0.2589773488280688</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0.5098001887748875</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.1251408883456446</v>
+        <v/>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.1251408883456446</v>
+        <v>0.2675857869455614</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.3380557805279382</v>
+        <v>0.2675857869455614</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0.5375089224738688</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2016</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.1186479316453869</v>
+        <v/>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.1186479316453869</v>
+        <v>0.2115496255976011</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.3335200591584981</v>
+        <v>0.2115496255976011</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.4351025887422955</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.1215515350025618</v>
+        <v/>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.1215515350025618</v>
+        <v>0.2353929656537501</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.338006371704117</v>
+        <v>0.2353929656537501</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.5107425490474619</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.1271113934919861</v>
+        <v/>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.1271113934919861</v>
+        <v>0.2332062332024128</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.3457901327501875</v>
+        <v>0.2332062332024128</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.5093001807560446</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.1216525595788837</v>
+        <v/>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.1216525595788837</v>
+        <v>0.2311391911654992</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.3461023295947343</v>
+        <v>0.2311391911654992</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.5029329790229849</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2020</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.1069429432751397</v>
+        <v/>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.1069429432751397</v>
+        <v>0.2356018085664341</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.3328428531343171</v>
+        <v>0.2356018085664341</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0.5470666003907639</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.1221964999181131</v>
+        <v/>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.1221964999181131</v>
+        <v>0.236795342516354</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.3562900560254143</v>
+        <v>0.236795342516354</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0.5830250408008254</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.1281794846170423</v>
+        <v/>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.1281794846170423</v>
+        <v>0.2450367334963822</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.36477366731481</v>
+        <v>0.2450367334963822</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.6034105205493679</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.1270962260179527</v>
+        <v/>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.1270962260179527</v>
+        <v>0.2413148692014937</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.3824923135098492</v>
+        <v>0.2413148692014937</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.5922998218931916</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.235409210231201</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.235409210231201</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.5678801361677024</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.2344434490809619</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.2344434490809619</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.5796363937506632</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.2292954898464945</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.2292954898464945</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.5649644056540338</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.2254441072050095</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.2254441072050095</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.566662909513546</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.2500640031288076</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.2500640031288076</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.7577571080303084</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.2440550966021886</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.2440550966021886</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.6796549448227914</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.2367680405887979</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.2367680405887979</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.6173859721946785</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.2335496175988593</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.2335496175988593</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.6032442444176603</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.237078231310455</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.237078231310455</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.613342808763505</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.2298733014214548</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.2298733014214548</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.5948778651225038</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.2311649351973324</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.2311649351973324</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.6394475522189885</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.2294273865354032</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.2294273865354032</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.6612299791297049</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.2291453116625567</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.2291453116625567</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.6531784889733858</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.2227652183841195</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.2227652183841195</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.6207982456295404</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.22118265538454</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.22118265538454</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.6457584768055189</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.2258261458526373</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.2258261458526373</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.7233713154342939</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.2259499722744766</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.2259499722744766</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.6755029588765633</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.2265714293934493</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.2265714293934493</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.660010598594947</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.2316980220851732</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.2316980220851732</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.7156502264523219</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B60" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0.1231845755982017</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0.1231845755982017</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.37754599357747</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.2325815551353715</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.2325815551353715</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.732524818206113</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1547,7 +2112,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100, stock-form primary)</t>
+          <t>Capacity-Adjusted Profit Rate (r*' = r*/u, DIVIDE; stock-form primary)</t>
         </is>
       </c>
     </row>
@@ -1607,7 +2172,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1967-1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -1619,7 +2184,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1728,44 +2293,52 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S514-AMULT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | deprecated_comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t># S514 - Capacity-Adjusted Profit Rate (r*_adj = r* x TCU/100)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t># S514 - Capacity-Adjusted Profit Rate (r*' = r*/u, DIVIDE)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension (stock-form primary, v1.2 Iter 3)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
+          <t>&lt;!-- status detail: stock-form primary; D1 2026-07-02 operation corrected multiply-&gt;divide --&gt;</t>
         </is>
       </c>
     </row>
@@ -1777,7 +2350,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
         </is>
       </c>
     </row>
@@ -1789,7 +2362,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marxian profit rate adjusted for capacity utilization. Isolates underlying-trend r* from cyclical variation in capital stock usage. Per Shaikh &amp; Tonak (1994), Chapter 5 p.124 and Table 5.11.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1801,31 +2374,39 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>Marxian profit rate adjusted for capacity utilization, isolating underlying-trend r*</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>from cyclical variation in capital-stock usage. Shaikh &amp; Tonak (1994) **Table 5.8**</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Derived: r*_adj = S513 x (TCU / 100).</t>
+          <t>defines it verbatim as **r*' = r*/u** (the profit rate is **DIVIDED** by capacity</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>utilization u). Book prose, Ch.5 p.124: "the mass of profit is divided by the rate of</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>- **Primary form (stock)**: S514-A uses S513-A (stock-form book r*); S514-EXT uses S513-EXT (stock-form extended r*). Form cascades automatically from S513's form choice; see `S513_DPR.md`.</t>
+          <t>capacity utilization, analogous to how actual output is divided by capacity utilization</t>
         </is>
       </c>
     </row>
@@ -1833,135 +2414,431 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- **Secondary form (flow)**: S514-FLOW = S513-FLOW x TCU/100. Retained as reference variant only; NOT used in S514-COMBINED.</t>
+          <t>to estimate potential output." **u is a fraction (0-1)**, u=1 = normal/full capacity.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>- TCU = Federal Reserve TCU series (cached at `data/raw/fred/fred_tcu_capacity_utilization.csv`).</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>&gt; **D1 correction (2026-07-02):** the prior v1.2 implementation MULTIPLIED (r*_adj = r* x</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>## Form-switch documentation</t>
+          <t>&gt; TCU/100), which ran below the book r*' and in the wrong conceptual direction (1989: old</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>&gt; 0.31 vs book 0.39). It is now the book's DIVIDE. The old multiplied series survives as the</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>v1.1 carried a hybrid splice that combined stock-form 1948-1989 and flow-form 1998-2024 inputs from S513. The v1.2 cohort (Iter 3) adopts stock-form primary across the entire 1948-2024 span; flow-form is retained as `S514-FLOW` secondary subseries (`_secondary: true`, `stage = secondary_variant`). See `VPR_S513_stock_vs_flow.md` and `VPR_S513_stock_vs_flow_DECISION_BRIEF.md` for the full methodological argument; DIV-012 records the cross-version discontinuity. S514's form choice has no independent degree of freedom: it is the TCU multiplication of whatever form S513 is in.</t>
+          <t>&gt; clearly-labelled DEPRECATED comparison subseries **S514-AMULT** (two-arm rule). See</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>&gt; `DIV-D02` in `DIVERGENCE_REGISTER.json` (patch: `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>## Coverage caveat</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TCU is available 1967-present. Pre-1967 years (1948-1966, 19 years) emit explicit NaN with `provenance: TCU NaN pre-1967` per the no-synthetic-data rule. Coverage gap 1990-1997 inherited from S513-EXT (BEA NIPA component series).</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Derived: **r*' = r* / u** (per arm):</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>## Anti-lazy-splice safeguard</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- **S514-A** (book period 1948-1989, PRIMARY): `S513-A / u_book`, where `u_book` is the book's</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>V03_S514 verifies r*_adj &lt;= r* (TCU &lt;= 100) and validates against registry reference values. The extension is recomputed each year from S513-EXT x TCU/100 rather than growth-rate-spliced from book r*_adj.</t>
+          <t xml:space="preserve">  OWN Shaikh-1992a utilization series (Table 5.8), a fraction, cached at</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  `data/source/book_tables/Table5_8_u_capacity_utilization.csv`. Full 1948-1989 coverage (the</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>## Validator</t>
+          <t xml:space="preserve">  old TCU-based arm had NaN pre-1967).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>- **S514-EXT** (1990-2024): `S513-EXT / (FRED TCU/100)`. FRED TCU is the constructible u-proxy</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stock-form S514-A: 23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj &lt;= r*. Benchmark anchors refreshed to stock-form values in `_v1.2_patches/S514_stockform_patch.json`.</t>
+          <t xml:space="preserve">  for the extension (the book's Shaikh-1992a series ends 1989). Source seam at 1989/1990 is</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  documented, not spliced (`DIV-D03`).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>- **S514-COMBINED**: S514-A (1948-1989) + S514-EXT (post-1989).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- **S514-FLOW** (secondary): `S513-FLOW / (FRED TCU/100)`. Flow-form reference variant only.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
+          <t>- **S514-AMULT** (DEPRECATED): `S513-A x TCU/100`, the retired multiply operation. Do not use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Form-switch documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>v1.1 carried a hybrid splice that combined stock-form 1948-1989 and flow-form 1998-2024 inputs from S513. The v1.2 cohort (Iter 3) adopts stock-form primary across the entire 1948-2024 span; flow-form is retained as `S514-FLOW` secondary subseries (`_secondary: true`, `stage = secondary_variant`). See `VPR_S513_stock_vs_flow.md` and `VPR_S513_stock_vs_flow_DECISION_BRIEF.md` for the full methodological argument; DIV-012 records the cross-version discontinuity. S514's form choice has no independent degree of freedom: it is the TCU multiplication of whatever form S513 is in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>## Coverage caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>The book arm S514-A now covers the full 1948-1989 (book's own u). The extension S514-EXT uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FRED TCU (1967-present); the 1990-1997 gap is inherited from S513-EXT (BEA NIPA SIC-&gt;NAICS bridge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>## Benchmarks and residual vs the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Reference values are the book's own **r*'** row (Table 5.8): 0.52 (1948), 0.47 (1958), 0.42 (1967),</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0.36 (1980), 0.39 (1989). New S514-A matches within the 0.01 rate tolerance at 1948 &amp; 1967; at 1958,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1980 &amp; 1989 it sits modestly above (0.49/0.38/0.42). That residual is **inherited from `DIV-D01`**</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>(the build's r* = S*/(K_net+V*) exceeds the book's r* = S*/K*_gross in later years — the S517</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>gross-vs-net gap), NOT a construction error. V03_S514 reports those three years as status</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>**DIVERGENCE** (registered) rather than FAIL; overall V03_S514 = PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>## Anti-lazy-splice safeguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>V03_S514 verifies the DIVIDE relationship actually holds (`S514-A == S513-A / u_book` to numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>precision) and checks the book r*' benchmarks. The extension is recomputed fresh each year from</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>`S513-EXT / (TCU/100)`, never growth-spliced from book r*'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Stock-form S514-A: 23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj &lt;= r*. Benchmark anchors refreshed to stock-form values in `_v1.2_patches/S514_stockform_patch.json`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>*Generated by anu-ingestion. Updated 2026-05-24 for v1.2 Iter 3 stock-form lockstep with S513.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>**EXT desync repaired (DIV-A16).** P02_S514 re-run against current S513: implied TCU multipliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>now 0.824/0.829/0.761 (1990/1998/2024); the impossible 1.415 @1990 (stale vintage) is gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OPEN (user-gated): capacity operation is r* x TCU/100 while the book publishes r*' = r*/u</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>(inverted); all three book-period refvals are tautological vs book 0.42/0.36/0.39 - decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>queued in WP-A_REGISTRY_PATCHES.json (S514-2).</t>
         </is>
       </c>
     </row>
@@ -2382,10 +3259,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2642,7 +3519,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"1967": 0.3635, "1980": 0.2621, "1989": 0.3118}</t>
+          <t>{"1948": 0.52, "1958": 0.47, "1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
         </is>
       </c>
     </row>
@@ -2727,6 +3604,54 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>v1.2 Iter 3 stock-form benchmarks: anchors at 1967/1980/1989 recomputed from S513-A (stock) x TCU/100. Old v1.1 anchors (1967=1.562, 1980=1.33, 1989=1.562) were wrong-scale percent-style values inconsistent with the rate units and stock-form denominator; replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>book_reference_values</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{"1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>validator_class_note</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pipeline_self; book Table 5.8 r*' recorded alongside (book_reference_values). Multiply-form capacity adjustment fails book benchmarks - see S514-2 user gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ext_refresh_note</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P02_S514 re-run 2026-07-01 against current S513; TCU multipliers now 0.824/0.829/0.761 (1990/1998/2024) - sane range (DIV-034). Repairs P31 DPR-drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>reference_values_source</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MWoN Table 5.8 r*' row (KB v2 _combined/5.8.csv). Years 1958/1980/1989 are registered-divergence (DIV-D02): build r*=S*/(K_net+V*) &gt; book r*=S*/K*_gross in later years; V03_S514 reports them DIVERGENCE not FAIL.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S514.xlsx
+++ b/extenbooks/S514.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -456,6 +456,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="53" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +490,11 @@
           <t>Derived: S513-FLOW × TCU/100, units=rate</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8 (r*'=r*/u, gross r*), units=rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -519,6 +525,11 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>S514-FLOW</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>S514-GROSS-A</t>
         </is>
       </c>
     </row>
@@ -541,6 +552,9 @@
       <c r="F3" s="3" t="n">
         <v/>
       </c>
+      <c r="G3" s="3" t="n">
+        <v>0.5202185792349726</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,6 +575,9 @@
       <c r="F4" s="3" t="n">
         <v/>
       </c>
+      <c r="G4" s="3" t="n">
+        <v>0.530591846933676</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -581,6 +598,9 @@
       <c r="F5" s="3" t="n">
         <v/>
       </c>
+      <c r="G5" s="3" t="n">
+        <v>0.4829537152308977</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,6 +621,9 @@
       <c r="F6" s="3" t="n">
         <v/>
       </c>
+      <c r="G6" s="3" t="n">
+        <v>0.4833764713132433</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -621,6 +644,9 @@
       <c r="F7" s="3" t="n">
         <v/>
       </c>
+      <c r="G7" s="3" t="n">
+        <v>0.4863990317530969</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -641,6 +667,9 @@
       <c r="F8" s="3" t="n">
         <v/>
       </c>
+      <c r="G8" s="3" t="n">
+        <v>0.4623550901560777</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -661,6 +690,9 @@
       <c r="F9" s="3" t="n">
         <v/>
       </c>
+      <c r="G9" s="3" t="n">
+        <v>0.4764738191138776</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -681,6 +713,9 @@
       <c r="F10" s="3" t="n">
         <v/>
       </c>
+      <c r="G10" s="3" t="n">
+        <v>0.454807768845021</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -701,6 +736,9 @@
       <c r="F11" s="3" t="n">
         <v/>
       </c>
+      <c r="G11" s="3" t="n">
+        <v>0.4338107686562245</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -721,6 +759,9 @@
       <c r="F12" s="3" t="n">
         <v/>
       </c>
+      <c r="G12" s="3" t="n">
+        <v>0.447949278358635</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -741,6 +782,9 @@
       <c r="F13" s="3" t="n">
         <v/>
       </c>
+      <c r="G13" s="3" t="n">
+        <v>0.4679453336085772</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -761,6 +805,9 @@
       <c r="F14" s="3" t="n">
         <v/>
       </c>
+      <c r="G14" s="3" t="n">
+        <v>0.4491224674151504</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -781,6 +828,9 @@
       <c r="F15" s="3" t="n">
         <v/>
       </c>
+      <c r="G15" s="3" t="n">
+        <v>0.4512687700460625</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -801,6 +851,9 @@
       <c r="F16" s="3" t="n">
         <v/>
       </c>
+      <c r="G16" s="3" t="n">
+        <v>0.4607649064144118</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -821,6 +874,9 @@
       <c r="F17" s="3" t="n">
         <v/>
       </c>
+      <c r="G17" s="3" t="n">
+        <v>0.4587385977957052</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -841,6 +897,9 @@
       <c r="F18" s="3" t="n">
         <v/>
       </c>
+      <c r="G18" s="3" t="n">
+        <v>0.4510016025641024</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -861,6 +920,9 @@
       <c r="F19" s="3" t="n">
         <v/>
       </c>
+      <c r="G19" s="3" t="n">
+        <v>0.4493620252478</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -881,6 +943,9 @@
       <c r="F20" s="3" t="n">
         <v/>
       </c>
+      <c r="G20" s="3" t="n">
+        <v>0.432329962983799</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -901,6 +966,9 @@
       <c r="F21" s="3" t="n">
         <v/>
       </c>
+      <c r="G21" s="3" t="n">
+        <v>0.4203333385389011</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +989,9 @@
       <c r="F22" s="3" t="n">
         <v>0.728559737739475</v>
       </c>
+      <c r="G22" s="3" t="n">
+        <v>0.419935863668709</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -941,6 +1012,9 @@
       <c r="F23" s="3" t="n">
         <v>0.7227529655585402</v>
       </c>
+      <c r="G23" s="3" t="n">
+        <v>0.4146496146496146</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -961,6 +1035,9 @@
       <c r="F24" s="3" t="n">
         <v>0.7066880107197617</v>
       </c>
+      <c r="G24" s="3" t="n">
+        <v>0.4005762829292241</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,6 +1058,9 @@
       <c r="F25" s="3" t="n">
         <v>0.7719031663740195</v>
       </c>
+      <c r="G25" s="3" t="n">
+        <v>0.4186887451645948</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1001,6 +1081,9 @@
       <c r="F26" s="3" t="n">
         <v>0.8035128186436683</v>
       </c>
+      <c r="G26" s="3" t="n">
+        <v>0.4240841715042728</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1021,6 +1104,9 @@
       <c r="F27" s="3" t="n">
         <v>0.7342731536491909</v>
       </c>
+      <c r="G27" s="3" t="n">
+        <v>0.3997250103801774</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1041,6 +1127,9 @@
       <c r="F28" s="3" t="n">
         <v>0.6746537947179896</v>
       </c>
+      <c r="G28" s="3" t="n">
+        <v>0.3864039495610644</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1061,6 +1150,9 @@
       <c r="F29" s="3" t="n">
         <v>0.6907168699825965</v>
       </c>
+      <c r="G29" s="3" t="n">
+        <v>0.362248008974162</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1081,6 +1173,9 @@
       <c r="F30" s="3" t="n">
         <v>0.798369791156025</v>
       </c>
+      <c r="G30" s="3" t="n">
+        <v>0.4123280876455182</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1101,6 +1196,9 @@
       <c r="F31" s="3" t="n">
         <v>0.7375046840129943</v>
       </c>
+      <c r="G31" s="3" t="n">
+        <v>0.3996346932512301</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1121,6 +1219,9 @@
       <c r="F32" s="3" t="n">
         <v>0.6900272000812439</v>
       </c>
+      <c r="G32" s="3" t="n">
+        <v>0.382657756721762</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1141,6 +1242,9 @@
       <c r="F33" s="3" t="n">
         <v>0.6720768013173983</v>
       </c>
+      <c r="G33" s="3" t="n">
+        <v>0.3634792465545868</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1161,6 +1265,9 @@
       <c r="F34" s="3" t="n">
         <v>0.6670724207386534</v>
       </c>
+      <c r="G34" s="3" t="n">
+        <v>0.3580018019225471</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1181,6 +1288,9 @@
       <c r="F35" s="3" t="n">
         <v>0.7080659143573559</v>
       </c>
+      <c r="G35" s="3" t="n">
+        <v>0.3552191250540344</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1201,6 +1311,9 @@
       <c r="F36" s="3" t="n">
         <v>0.7351653492189895</v>
       </c>
+      <c r="G36" s="3" t="n">
+        <v>0.3608373414594683</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1221,6 +1334,9 @@
       <c r="F37" s="3" t="n">
         <v>0.8072303142166534</v>
       </c>
+      <c r="G37" s="3" t="n">
+        <v>0.3822781533049146</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1241,6 +1357,9 @@
       <c r="F38" s="3" t="n">
         <v>0.809248384863314</v>
       </c>
+      <c r="G38" s="3" t="n">
+        <v>0.3644456382978805</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1261,6 +1380,9 @@
       <c r="F39" s="3" t="n">
         <v>0.7619331514059144</v>
       </c>
+      <c r="G39" s="3" t="n">
+        <v>0.3671045548278699</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1281,6 +1403,9 @@
       <c r="F40" s="3" t="n">
         <v>0.7943325624234238</v>
       </c>
+      <c r="G40" s="3" t="n">
+        <v>0.3784187581830618</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1301,6 +1426,9 @@
       <c r="F41" s="3" t="n">
         <v>0.834570272406301</v>
       </c>
+      <c r="G41" s="3" t="n">
+        <v>0.4003156363359909</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1321,6 +1449,9 @@
       <c r="F42" s="3" t="n">
         <v>0.816565883745027</v>
       </c>
+      <c r="G42" s="3" t="n">
+        <v>0.3949976396110434</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1341,6 +1472,9 @@
       <c r="F43" s="3" t="n">
         <v>0.7657491255489522</v>
       </c>
+      <c r="G43" s="3" t="n">
+        <v>0.3873911451442171</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1361,6 +1495,9 @@
       <c r="F44" s="3" t="n">
         <v>0.7837212015131731</v>
       </c>
+      <c r="G44" s="3" t="n">
+        <v>0.3942937435944095</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1381,6 +1518,9 @@
       <c r="F45" s="3" t="n">
         <v>0.464994592247802</v>
       </c>
+      <c r="G45" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1401,6 +1541,9 @@
       <c r="F46" s="3" t="n">
         <v>0.4744180672365246</v>
       </c>
+      <c r="G46" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1421,6 +1564,9 @@
       <c r="F47" s="3" t="n">
         <v>0.4788620574070779</v>
       </c>
+      <c r="G47" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1441,6 +1587,9 @@
       <c r="F48" s="3" t="n">
         <v>0.4839554224164071</v>
       </c>
+      <c r="G48" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1461,6 +1610,9 @@
       <c r="F49" s="3" t="n">
         <v>0.5003136556218815</v>
       </c>
+      <c r="G49" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1481,6 +1633,9 @@
       <c r="F50" s="3" t="n">
         <v>0.5098001887748875</v>
       </c>
+      <c r="G50" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1501,6 +1656,9 @@
       <c r="F51" s="3" t="n">
         <v>0.5375089224738688</v>
       </c>
+      <c r="G51" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1521,6 +1679,9 @@
       <c r="F52" s="3" t="n">
         <v>0.4351025887422955</v>
       </c>
+      <c r="G52" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1541,6 +1702,9 @@
       <c r="F53" s="3" t="n">
         <v>0.5107425490474619</v>
       </c>
+      <c r="G53" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1561,6 +1725,9 @@
       <c r="F54" s="3" t="n">
         <v>0.5093001807560446</v>
       </c>
+      <c r="G54" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1581,6 +1748,9 @@
       <c r="F55" s="3" t="n">
         <v>0.5029329790229849</v>
       </c>
+      <c r="G55" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1601,6 +1771,9 @@
       <c r="F56" s="3" t="n">
         <v>0.5470666003907639</v>
       </c>
+      <c r="G56" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1621,6 +1794,9 @@
       <c r="F57" s="3" t="n">
         <v>0.5830250408008254</v>
       </c>
+      <c r="G57" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1641,6 +1817,9 @@
       <c r="F58" s="3" t="n">
         <v>0.6034105205493679</v>
       </c>
+      <c r="G58" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1661,6 +1840,9 @@
       <c r="F59" s="3" t="n">
         <v>0.5922998218931916</v>
       </c>
+      <c r="G59" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1681,6 +1863,9 @@
       <c r="F60" s="3" t="n">
         <v>0.5678801361677024</v>
       </c>
+      <c r="G60" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1701,6 +1886,9 @@
       <c r="F61" s="3" t="n">
         <v>0.5796363937506632</v>
       </c>
+      <c r="G61" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1721,6 +1909,9 @@
       <c r="F62" s="3" t="n">
         <v>0.5649644056540338</v>
       </c>
+      <c r="G62" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1741,6 +1932,9 @@
       <c r="F63" s="3" t="n">
         <v>0.566662909513546</v>
       </c>
+      <c r="G63" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1761,6 +1955,9 @@
       <c r="F64" s="3" t="n">
         <v>0.7577571080303084</v>
       </c>
+      <c r="G64" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1781,6 +1978,9 @@
       <c r="F65" s="3" t="n">
         <v>0.6796549448227914</v>
       </c>
+      <c r="G65" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1801,6 +2001,9 @@
       <c r="F66" s="3" t="n">
         <v>0.6173859721946785</v>
       </c>
+      <c r="G66" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1821,6 +2024,9 @@
       <c r="F67" s="3" t="n">
         <v>0.6032442444176603</v>
       </c>
+      <c r="G67" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1841,6 +2047,9 @@
       <c r="F68" s="3" t="n">
         <v>0.613342808763505</v>
       </c>
+      <c r="G68" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1861,6 +2070,9 @@
       <c r="F69" s="3" t="n">
         <v>0.5948778651225038</v>
       </c>
+      <c r="G69" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1881,6 +2093,9 @@
       <c r="F70" s="3" t="n">
         <v>0.6394475522189885</v>
       </c>
+      <c r="G70" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1901,6 +2116,9 @@
       <c r="F71" s="3" t="n">
         <v>0.6612299791297049</v>
       </c>
+      <c r="G71" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1921,6 +2139,9 @@
       <c r="F72" s="3" t="n">
         <v>0.6531784889733858</v>
       </c>
+      <c r="G72" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1941,6 +2162,9 @@
       <c r="F73" s="3" t="n">
         <v>0.6207982456295404</v>
       </c>
+      <c r="G73" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1961,6 +2185,9 @@
       <c r="F74" s="3" t="n">
         <v>0.6457584768055189</v>
       </c>
+      <c r="G74" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1981,6 +2208,9 @@
       <c r="F75" s="3" t="n">
         <v>0.7233713154342939</v>
       </c>
+      <c r="G75" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2001,6 +2231,9 @@
       <c r="F76" s="3" t="n">
         <v>0.6755029588765633</v>
       </c>
+      <c r="G76" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2021,6 +2254,9 @@
       <c r="F77" s="3" t="n">
         <v>0.660010598594947</v>
       </c>
+      <c r="G77" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2041,6 +2277,9 @@
       <c r="F78" s="3" t="n">
         <v>0.7156502264523219</v>
       </c>
+      <c r="G78" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2060,6 +2299,9 @@
       </c>
       <c r="F79" s="3" t="n">
         <v>0.732524818206113</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2305,84 +2547,88 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S514-GROSS-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8 (r*'=r*/u, gross r*) | variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t># S514 - Capacity-Adjusted Profit Rate (r*' = r*/u, DIVIDE)</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S514 - Capacity-Adjusted Profit Rate (r*' = r*/u, DIVIDE)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>&lt;!-- status detail: stock-form primary; D1 2026-07-02 operation corrected multiply-&gt;divide --&gt;</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>&lt;!-- status detail: stock-form primary; D1 2026-07-02 operation corrected multiply-&gt;divide --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marxian profit rate adjusted for capacity utilization, isolating underlying-trend r*</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>from cyclical variation in capital-stock usage. Shaikh &amp; Tonak (1994) **Table 5.8**</t>
+          <t>Marxian profit rate adjusted for capacity utilization, isolating underlying-trend r*</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2636,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>defines it verbatim as **r*' = r*/u** (the profit rate is **DIVIDED** by capacity</t>
+          <t>from cyclical variation in capital-stock usage. Shaikh &amp; Tonak (1994) **Table 5.8**</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2644,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>utilization u). Book prose, Ch.5 p.124: "the mass of profit is divided by the rate of</t>
+          <t>defines it verbatim as **r*' = r*/u** (the profit rate is **DIVIDED** by capacity</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2652,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>capacity utilization, analogous to how actual output is divided by capacity utilization</t>
+          <t>utilization u). Book prose, Ch.5 p.124: "the mass of profit is divided by the rate of</t>
         </is>
       </c>
     </row>
@@ -2414,27 +2660,27 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>to estimate potential output." **u is a fraction (0-1)**, u=1 = normal/full capacity.</t>
+          <t>capacity utilization, analogous to how actual output is divided by capacity utilization</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>to estimate potential output." **u is a fraction (0-1)**, u=1 = normal/full capacity.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>&gt; **D1 correction (2026-07-02):** the prior v1.2 implementation MULTIPLIED (r*_adj = r* x</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>&gt; TCU/100), which ran below the book r*' and in the wrong conceptual direction (1989: old</t>
+          <t>&gt; **D1 correction (2026-07-02):** the prior v1.2 implementation MULTIPLIED (r*_adj = r* x</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2688,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>&gt; 0.31 vs book 0.39). It is now the book's DIVIDE. The old multiplied series survives as the</t>
+          <t>&gt; TCU/100), which ran below the book r*' and in the wrong conceptual direction (1989: old</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2696,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>&gt; clearly-labelled DEPRECATED comparison subseries **S514-AMULT** (two-arm rule). See</t>
+          <t>&gt; 0.31 vs book 0.39). It is now the book's DIVIDE. The old multiplied series survives as the</t>
         </is>
       </c>
     </row>
@@ -2458,51 +2704,51 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>&gt; `DIV-D02` in `DIVERGENCE_REGISTER.json` (patch: `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`).</t>
+          <t>&gt; clearly-labelled DEPRECATED comparison subseries **S514-AMULT** (two-arm rule). See</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>&gt; `DIV-D02` in `DIVERGENCE_REGISTER.json` (patch: `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Derived: **r*' = r* / u** (per arm):</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Derived: **r*' = r* / u** (per arm):</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- **S514-A** (book period 1948-1989, PRIMARY): `S513-A / u_book`, where `u_book` is the book's</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  OWN Shaikh-1992a utilization series (Table 5.8), a fraction, cached at</t>
+          <t>- **S514-A** (book period 1948-1989, PRIMARY): `S513-A / u_book`, where `u_book` is the book's</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2756,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  `data/source/book_tables/Table5_8_u_capacity_utilization.csv`. Full 1948-1989 coverage (the</t>
+          <t xml:space="preserve">  OWN Shaikh-1992a utilization series (Table 5.8), a fraction, cached at</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2764,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  old TCU-based arm had NaN pre-1967).</t>
+          <t xml:space="preserve">  `data/source/book_tables/Table5_8_u_capacity_utilization.csv`. Full 1948-1989 coverage (the</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2772,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- **S514-EXT** (1990-2024): `S513-EXT / (FRED TCU/100)`. FRED TCU is the constructible u-proxy</t>
+          <t xml:space="preserve">  old TCU-based arm had NaN pre-1967).</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2780,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  for the extension (the book's Shaikh-1992a series ends 1989). Source seam at 1989/1990 is</t>
+          <t>- **S514-EXT** (1990-2024): `S513-EXT / (FRED TCU/100)`. FRED TCU is the constructible u-proxy</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2788,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  documented, not spliced (`DIV-D03`).</t>
+          <t xml:space="preserve">  for the extension (the book's Shaikh-1992a series ends 1989). Source seam at 1989/1990 is</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2796,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- **S514-COMBINED**: S514-A (1948-1989) + S514-EXT (post-1989).</t>
+          <t xml:space="preserve">  documented, not spliced (`DIV-D03`).</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2804,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- **S514-FLOW** (secondary): `S513-FLOW / (FRED TCU/100)`. Flow-form reference variant only.</t>
+          <t>- **S514-COMBINED**: S514-A (1948-1989) + S514-EXT (post-1989).</t>
         </is>
       </c>
     </row>
@@ -2566,95 +2812,95 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **S514-AMULT** (DEPRECATED): `S513-A x TCU/100`, the retired multiply operation. Do not use.</t>
+          <t>- **S514-FLOW** (secondary): `S513-FLOW / (FRED TCU/100)`. Flow-form reference variant only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- **S514-AMULT** (DEPRECATED): `S513-A x TCU/100`, the retired multiply operation. Do not use.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>## Form-switch documentation</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Form-switch documentation</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>v1.1 carried a hybrid splice that combined stock-form 1948-1989 and flow-form 1998-2024 inputs from S513. The v1.2 cohort (Iter 3) adopts stock-form primary across the entire 1948-2024 span; flow-form is retained as `S514-FLOW` secondary subseries (`_secondary: true`, `stage = secondary_variant`). See `VPR_S513_stock_vs_flow.md` and `VPR_S513_stock_vs_flow_DECISION_BRIEF.md` for the full methodological argument; DIV-012 records the cross-version discontinuity. S514's form choice has no independent degree of freedom: it is the TCU multiplication of whatever form S513 is in.</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>v1.1 carried a hybrid splice that combined stock-form 1948-1989 and flow-form 1998-2024 inputs from S513. The v1.2 cohort (Iter 3) adopts stock-form primary across the entire 1948-2024 span; flow-form is retained as `S514-FLOW` secondary subseries (`_secondary: true`, `stage = secondary_variant`). See `VPR_S513_stock_vs_flow.md` and `VPR_S513_stock_vs_flow_DECISION_BRIEF.md` for the full methodological argument; DIV-012 records the cross-version discontinuity. S514's form choice has no independent degree of freedom: it is the TCU multiplication of whatever form S513 is in.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>## Coverage caveat</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>## Coverage caveat</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>The book arm S514-A now covers the full 1948-1989 (book's own u). The extension S514-EXT uses</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRED TCU (1967-present); the 1990-1997 gap is inherited from S513-EXT (BEA NIPA SIC-&gt;NAICS bridge).</t>
+          <t>The book arm S514-A now covers the full 1948-1989 (book's own u). The extension S514-EXT uses</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FRED TCU (1967-present); the 1990-1997 gap is inherited from S513-EXT (BEA NIPA SIC-&gt;NAICS bridge).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>## Benchmarks and residual vs the book</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>## Benchmarks and residual vs the book</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Reference values are the book's own **r*'** row (Table 5.8): 0.52 (1948), 0.47 (1958), 0.42 (1967),</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0.36 (1980), 0.39 (1989). New S514-A matches within the 0.01 rate tolerance at 1948 &amp; 1967; at 1958,</t>
+          <t>Reference values are the book's own **r*'** row (Table 5.8): 0.52 (1948), 0.47 (1958), 0.42 (1967),</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2908,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1980 &amp; 1989 it sits modestly above (0.49/0.38/0.42). That residual is **inherited from `DIV-D01`**</t>
+          <t>0.36 (1980), 0.39 (1989). New S514-A matches within the 0.01 rate tolerance at 1948 &amp; 1967; at 1958,</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2916,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(the build's r* = S*/(K_net+V*) exceeds the book's r* = S*/K*_gross in later years — the S517</t>
+          <t>1980 &amp; 1989 it sits modestly above (0.49/0.38/0.42). That residual is **inherited from `DIV-D01`**</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2924,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gross-vs-net gap), NOT a construction error. V03_S514 reports those three years as status</t>
+          <t>(the build's r* = S*/(K_net+V*) exceeds the book's r* = S*/K*_gross in later years — the S517</t>
         </is>
       </c>
     </row>
@@ -2686,39 +2932,39 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>**DIVERGENCE** (registered) rather than FAIL; overall V03_S514 = PASS.</t>
+          <t>gross-vs-net gap), NOT a construction error. V03_S514 reports those three years as status</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>**DIVERGENCE** (registered) rather than FAIL; overall V03_S514 = PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>## Anti-lazy-splice safeguard</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Anti-lazy-splice safeguard</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>V03_S514 verifies the DIVIDE relationship actually holds (`S514-A == S513-A / u_book` to numerical</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>precision) and checks the book r*' benchmarks. The extension is recomputed fresh each year from</t>
+          <t>V03_S514 verifies the DIVIDE relationship actually holds (`S514-A == S513-A / u_book` to numerical</t>
         </is>
       </c>
     </row>
@@ -2726,87 +2972,87 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>`S513-EXT / (TCU/100)`, never growth-spliced from book r*'.</t>
+          <t>precision) and checks the book r*' benchmarks. The extension is recomputed fresh each year from</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>`S513-EXT / (TCU/100)`, never growth-spliced from book r*'.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>## Validator</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Stock-form S514-A: 23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj &lt;= r*. Benchmark anchors refreshed to stock-form values in `_v1.2_patches/S514_stockform_patch.json`.</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Stock-form S514-A: 23 valid years (1967-1989), 19 NaN pre-1967. All valid years satisfy r*_adj &lt;= r*. Benchmark anchors refreshed to stock-form values in `_v1.2_patches/S514_stockform_patch.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion. Updated 2026-05-24 for v1.2 Iter 3 stock-form lockstep with S513.*</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion. Updated 2026-05-24 for v1.2 Iter 3 stock-form lockstep with S513.*</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>**EXT desync repaired (DIV-A16).** P02_S514 re-run against current S513: implied TCU multipliers</t>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3060,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>now 0.824/0.829/0.761 (1990/1998/2024); the impossible 1.415 @1990 (stale vintage) is gone.</t>
+          <t>**EXT desync repaired (DIV-A16).** P02_S514 re-run against current S513: implied TCU multipliers</t>
         </is>
       </c>
     </row>
@@ -2822,7 +3068,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OPEN (user-gated): capacity operation is r* x TCU/100 while the book publishes r*' = r*/u</t>
+          <t>now 0.824/0.829/0.761 (1990/1998/2024); the impossible 1.415 @1990 (stale vintage) is gone.</t>
         </is>
       </c>
     </row>
@@ -2830,7 +3076,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>(inverted); all three book-period refvals are tautological vs book 0.42/0.36/0.39 - decision</t>
+          <t>OPEN (user-gated): capacity operation is r* x TCU/100 while the book publishes r*' = r*/u</t>
         </is>
       </c>
     </row>
@@ -2838,7 +3084,51 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
+          <t>(inverted); all three book-period refvals are tautological vs book 0.42/0.36/0.39 - decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>queued in WP-A_REGISTRY_PATCHES.json (S514-2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>## Book-period Gross-K* variant (added 2026-07-07, K-plan WP-K4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>**Subseries `S514-GROSS-A`** (book period 1948-1989 only, `nan` beyond). Book-faithful r*' = r*_gross/u (DIVIDE) = the book's OWN published r*' (reproduces Table 5.8 to MAE 0.0023). No DIVERGENCE bucket needed (unlike the net S514-A), which is the point: the gross variant is book-faithful by construction. See `VPR_S514_gross_book` in the registry, `DIVERGENCE_REGISTER.json` **DIV-070** (+ narrowed **DIV-058**), and `Handoffs/REVIEW_2026-07-07/F2_KSTAR_FIDELITY.md`. Additive only — the primary net series is unchanged; current-$ gross is non-constructible 1990-&gt; (BEA discontinued current-cost gross at the 1997 revision), so there is no extension.</t>
         </is>
       </c>
     </row>
@@ -3259,14 +3549,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3394,163 +3684,176 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S513-GROSS-A, Table5_8_u_capacity_utilization.csv</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S514-GROSS-A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>r*'_gross = S513-GROSS-A / u_book (DIVIDE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FRED</t>
-        </is>
-      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>FRED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S514-EXT</t>
+          <t>derive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S514-COMBINED</t>
+          <t>S514-EXT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>stock_primary_v1.2</t>
+          <t>S514-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>form</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations*. Cambridge University Press., Chapter 5, Table 5.11 (capacity-adjusted profit rate r*_adj = r* x TCU/100, 1967-1989 due to TCU data availability); Figure 5.11. Stock-form r* per p.122 \u00a75.5 verbatim definition.", "shaikh_appendix_ref": "Table 5.11 r*_adj column; TCU from Federal Reserve G.17 (1967-present)", "extension_source": "FRED TCU (Total Capacity Utilization, all industries): identifier TCU; multiplied by S513 (Marxian profit rate, stock-form)", "extension_url": "https://fred.stlouisfed.org/series/TCU", "conceptual_continuity": "Capacity-adjusted profit rate r*_adj = r* x TCU/100 adjusts the Marxian profit rate by current capacity utilization, isolating the structural component from cyclical fluctuations in capital usage. It is a derived product of S513 (stock-form) and a directly observable utilization series (FRED TCU). Conceptual continuity is high because FRED TCU is the canonical capacity-utilization series and has been continuously published since 1967.", "vintage_note": "FRED TCU methodology was revised in 2002 (G.17 Industrial Production redesign); pre-2002 values are not strictly comparable. r*_adj vintage divergence is dominated by S513's vintage issues (BEA 2013 R&amp;D capitalization through S517 in the stock-form denominator).", "form_change_note": "v1.2 Iter 3: cascades S513 stock-form primary adoption. Flow-form retained as S514-FLOW secondary subseries only. See DIV-012 and VPR_S513_stock_vs_flow_DECISION_BRIEF."}</t>
+          <t>stock_primary_v1.2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations*. Cambridge University Press., Chapter 5, Table 5.11 (capacity-adjusted profit rate r*_adj = r* x TCU/100, 1967-1989 due to TCU data availability); Figure 5.11. Stock-form r* per p.122 \u00a75.5 verbatim definition.", "shaikh_appendix_ref": "Table 5.11 r*_adj column; TCU from Federal Reserve G.17 (1967-present)", "extension_source": "FRED TCU (Total Capacity Utilization, all industries): identifier TCU; multiplied by S513 (Marxian profit rate, stock-form)", "extension_url": "https://fred.stlouisfed.org/series/TCU", "conceptual_continuity": "Capacity-adjusted profit rate r*_adj = r* x TCU/100 adjusts the Marxian profit rate by current capacity utilization, isolating the structural component from cyclical fluctuations in capital usage. It is a derived product of S513 (stock-form) and a directly observable utilization series (FRED TCU). Conceptual continuity is high because FRED TCU is the canonical capacity-utilization series and has been continuously published since 1967.", "vintage_note": "FRED TCU methodology was revised in 2002 (G.17 Industrial Production redesign); pre-2002 values are not strictly comparable. r*_adj vintage divergence is dominated by S513's vintage issues (BEA 2013 R&amp;D capitalization through S517 in the stock-form denominator).", "form_change_note": "v1.2 Iter 3: cascades S513 stock-form primary adoption. Flow-form retained as S514-FLOW secondary subseries only. See DIV-012 and VPR_S513_stock_vs_flow_DECISION_BRIEF."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>depends_on</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>["S513"]</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{"1948": 0.52, "1958": 0.47, "1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>{"1948": 0.52, "1958": 0.47, "1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3562,96 +3865,132 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>extension_year_range</t>
+          <t>tolerance_abs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1948, 2024]</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>extension_year_range</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>v1.2 Iter 3 stock-form benchmarks: anchors at 1967/1980/1989 recomputed from S513-A (stock) x TCU/100. Old v1.1 anchors (1967=1.562, 1980=1.33, 1989=1.562) were wrong-scale percent-style values inconsistent with the rate units and stock-form denominator; replaced.</t>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>book_reference_values</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{"1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
+          <t>v1.2 Iter 3 stock-form benchmarks: anchors at 1967/1980/1989 recomputed from S513-A (stock) x TCU/100. Old v1.1 anchors (1967=1.562, 1980=1.33, 1989=1.562) were wrong-scale percent-style values inconsistent with the rate units and stock-form denominator; replaced.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>validator_class_note</t>
+          <t>book_reference_values</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pipeline_self; book Table 5.8 r*' recorded alongside (book_reference_values). Multiply-form capacity adjustment fails book benchmarks - see S514-2 user gate.</t>
+          <t>{"1967": 0.42, "1980": 0.36, "1989": 0.39}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ext_refresh_note</t>
+          <t>validator_class_note</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P02_S514 re-run 2026-07-01 against current S513; TCU multipliers now 0.824/0.829/0.761 (1990/1998/2024) - sane range (DIV-034). Repairs P31 DPR-drift.</t>
+          <t>pipeline_self; book Table 5.8 r*' recorded alongside (book_reference_values). Multiply-form capacity adjustment fails book benchmarks - see S514-2 user gate.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>ext_refresh_note</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P02_S514 re-run 2026-07-01 against current S513; TCU multipliers now 0.824/0.829/0.761 (1990/1998/2024) - sane range (DIV-034). Repairs P31 DPR-drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>reference_values_source</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>MWoN Table 5.8 r*' row (KB v2 _combined/5.8.csv). Years 1958/1980/1989 are registered-divergence (DIV-D02): build r*=S*/(K_net+V*) &gt; book r*=S*/K*_gross in later years; V03_S514 reports them DIVERGENCE not FAIL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>variant_reference_values</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{"S514-GROSS-A": {"1948": 0.52, "1949": 0.53, "1950": 0.48, "1951": 0.49, "1952": 0.49, "1953": 0.46, "1954": 0.48, "1955": 0.46, "1956": 0.43, "1957": 0.45, "1958": 0.47, "1959": 0.45, "1960": 0.45, "1961": 0.46, "1962": 0.46, "1963": 0.45, "1964": 0.45, "1965": 0.43, "1966": 0.42, "1967": 0.42, "1968": 0.41, "1969": 0.4, "1970": 0.42, "1971": 0.42, "1972": 0.4, "1973": 0.39, "1974": 0.36, "1975": 0.41, "1976": 0.4, "1977": 0.38, "1978": 0.36, "1979": 0.36, "1980": 0.36, "1981": 0.36, "1982": 0.38, "1983": 0.36, "1984": 0.37, "1985": 0.38, "1986": 0.4, "1987": 0.39, "1988": 0.39, "1989": 0.39}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>variant_reference_values_note</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S514-GROSS-A = book Table 5.8 published r*' (r*_gross/u), full column. Build reproduces it to MAE 0.0023; 40/42 years EXACT at printed 2dp (1951,1955 off by 0.01). Book-anchored INDEPENDENT reference values (printed book Table 5.8 / 5.7 / 5.11 cells, KB v2 _combined/5.8.csv; full 1948-1989 column). Checked by V03 against the S*-GROSS-A book-faithful variant. Unlike validation.reference_values (tautological = loader output, A1), these are the book's OWN published numbers -&gt; the r*/r*' family's first independent book anchor (F2 2026-07-07, K-plan WP-K3).</t>
         </is>
       </c>
     </row>
